--- a/单打评分实验记录_男1450女1300.xlsx
+++ b/单打评分实验记录_男1450女1300.xlsx
@@ -488,7 +488,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>中央民族大学匹克球俱乐部 · 单打评分实验记录</t>
+          <t>中央民族大学石榴籽体育管理 · 单打评分实验记录</t>
         </is>
       </c>
     </row>
